--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N57_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0002T0006Z000C1N57_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.30671226789914</v>
+        <v>3.787340743533611</v>
       </c>
       <c r="D2" t="n">
-        <v>23.15615392509511</v>
+        <v>3.762875012827956</v>
       </c>
       <c r="E2" t="n">
-        <v>10.06788922629623</v>
+        <v>1.636031999273138</v>
       </c>
       <c r="F2" t="n">
-        <v>11.18714162886494</v>
+        <v>1.817910514690552</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>43.44249072049161</v>
+        <v>7.059404742079887</v>
       </c>
       <c r="D3" t="n">
-        <v>45.53043718282498</v>
+        <v>7.39869604220906</v>
       </c>
       <c r="E3" t="n">
-        <v>10.06788922629623</v>
+        <v>1.636031999273138</v>
       </c>
       <c r="F3" t="n">
-        <v>11.18714162886494</v>
+        <v>1.817910514690552</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
